--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-07-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE4691D-2D8E-4010-9ECC-608A35070599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3777B8C9-5F20-4EB0-8EF8-C21CDB646A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="840" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="394">
   <si>
     <t>SKU</t>
   </si>
@@ -1190,6 +1190,18 @@
   </si>
   <si>
     <t>£1,610.05</t>
+  </si>
+  <si>
+    <t>£18.10</t>
+  </si>
+  <si>
+    <t>£59.61</t>
+  </si>
+  <si>
+    <t>£41.66</t>
+  </si>
+  <si>
+    <t>£52.00</t>
   </si>
 </sst>
 </file>
@@ -1675,13 +1687,13 @@
         <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>390</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>390</v>
       </c>
       <c r="F3" t="s">
         <v>345</v>
@@ -2291,13 +2303,13 @@
         <v>167</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>391</v>
       </c>
       <c r="D14" t="s">
         <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>168</v>
+        <v>391</v>
       </c>
       <c r="F14" t="s">
         <v>191</v>
@@ -2353,7 +2365,7 @@
         <v>179</v>
       </c>
       <c r="E15" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="F15" t="s">
         <v>354</v>
@@ -2571,13 +2583,13 @@
         <v>225</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>392</v>
       </c>
       <c r="D19" t="s">
         <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>392</v>
       </c>
       <c r="F19" t="s">
         <v>357</v>
@@ -2627,13 +2639,13 @@
         <v>237</v>
       </c>
       <c r="C20" t="s">
-        <v>238</v>
+        <v>393</v>
       </c>
       <c r="D20" t="s">
         <v>238</v>
       </c>
       <c r="E20" t="s">
-        <v>238</v>
+        <v>393</v>
       </c>
       <c r="F20" t="s">
         <v>358</v>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-07-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A49A367-F762-4D65-95C2-23BF92ADDFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD2CC6F-55C3-4D52-87C2-7FED3A942177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4710" yWindow="2400" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32985" yWindow="2475" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -823,9 +823,6 @@
     <t>£69.55</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/50mm-celotex-cw4050-cavity-insulation-1200mm-x-450mm-11-boards</t>
-  </si>
-  <si>
     <t>cw40755</t>
   </si>
   <si>
@@ -850,9 +847,6 @@
     <t>£66.32</t>
   </si>
   <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/75mm-celotex-cw4075-cavity-insulation-1200mm-x-450mm-8-boards</t>
-  </si>
-  <si>
     <t>celcav85</t>
   </si>
   <si>
@@ -1205,6 +1199,12 @@
   </si>
   <si>
     <t>£1972.64</t>
+  </si>
+  <si>
+    <t>£76.12</t>
+  </si>
+  <si>
+    <t>£74.93</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1643,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G2" t="s">
         <v>22</v>
@@ -1667,10 +1667,10 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="O2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="P2" t="s">
         <v>28</v>
@@ -1690,16 +1690,16 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G3" t="s">
         <v>34</v>
@@ -1723,10 +1723,10 @@
         <v>38</v>
       </c>
       <c r="N3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="O3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P3" t="s">
         <v>33</v>
@@ -1746,16 +1746,16 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G4" t="s">
         <v>44</v>
@@ -1779,7 +1779,7 @@
         <v>49</v>
       </c>
       <c r="N4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="O4" t="s">
         <v>43</v>
@@ -1811,7 +1811,7 @@
         <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G5" t="s">
         <v>56</v>
@@ -1835,7 +1835,7 @@
         <v>61</v>
       </c>
       <c r="N5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="O5" t="s">
         <v>55</v>
@@ -1867,7 +1867,7 @@
         <v>67</v>
       </c>
       <c r="F6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G6" t="s">
         <v>68</v>
@@ -1891,10 +1891,10 @@
         <v>73</v>
       </c>
       <c r="N6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="O6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P6" t="s">
         <v>75</v>
@@ -1914,16 +1914,16 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G7" t="s">
         <v>81</v>
@@ -1947,7 +1947,7 @@
         <v>85</v>
       </c>
       <c r="N7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O7" t="s">
         <v>90</v>
@@ -1970,16 +1970,16 @@
         <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G8" t="s">
         <v>81</v>
@@ -2003,7 +2003,7 @@
         <v>94</v>
       </c>
       <c r="N8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O8" t="s">
         <v>90</v>
@@ -2035,7 +2035,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G9" t="s">
         <v>101</v>
@@ -2059,10 +2059,10 @@
         <v>106</v>
       </c>
       <c r="N9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="O9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="P9" t="s">
         <v>107</v>
@@ -2082,16 +2082,16 @@
         <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G10" t="s">
         <v>112</v>
@@ -2115,10 +2115,10 @@
         <v>117</v>
       </c>
       <c r="N10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P10" t="s">
         <v>118</v>
@@ -2138,16 +2138,16 @@
         <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F11" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G11" t="s">
         <v>124</v>
@@ -2171,7 +2171,7 @@
         <v>128</v>
       </c>
       <c r="N11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="O11" t="s">
         <v>123</v>
@@ -2203,7 +2203,7 @@
         <v>135</v>
       </c>
       <c r="F12" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G12" t="s">
         <v>135</v>
@@ -2227,7 +2227,7 @@
         <v>140</v>
       </c>
       <c r="N12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="O12" t="s">
         <v>134</v>
@@ -2250,16 +2250,16 @@
         <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F13" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G13" t="s">
         <v>146</v>
@@ -2283,7 +2283,7 @@
         <v>151</v>
       </c>
       <c r="N13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="O13" t="s">
         <v>145</v>
@@ -2306,16 +2306,16 @@
         <v>156</v>
       </c>
       <c r="C14" t="s">
+        <v>325</v>
+      </c>
+      <c r="D14" t="s">
+        <v>325</v>
+      </c>
+      <c r="E14" t="s">
+        <v>325</v>
+      </c>
+      <c r="F14" t="s">
         <v>327</v>
-      </c>
-      <c r="D14" t="s">
-        <v>327</v>
-      </c>
-      <c r="E14" t="s">
-        <v>327</v>
-      </c>
-      <c r="F14" t="s">
-        <v>329</v>
       </c>
       <c r="G14" t="s">
         <v>158</v>
@@ -2339,7 +2339,7 @@
         <v>163</v>
       </c>
       <c r="N14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="O14" t="s">
         <v>157</v>
@@ -2362,16 +2362,16 @@
         <v>167</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E15" t="s">
         <v>136</v>
       </c>
       <c r="F15" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G15" t="s">
         <v>169</v>
@@ -2418,16 +2418,16 @@
         <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F16" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G16" t="s">
         <v>180</v>
@@ -2451,7 +2451,7 @@
         <v>185</v>
       </c>
       <c r="N16" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="O16" t="s">
         <v>179</v>
@@ -2483,7 +2483,7 @@
         <v>191</v>
       </c>
       <c r="F17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G17" t="s">
         <v>136</v>
@@ -2507,10 +2507,10 @@
         <v>195</v>
       </c>
       <c r="N17" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="O17" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="P17" t="s">
         <v>196</v>
@@ -2539,7 +2539,7 @@
         <v>200</v>
       </c>
       <c r="F18" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G18" t="s">
         <v>201</v>
@@ -2563,10 +2563,10 @@
         <v>206</v>
       </c>
       <c r="N18" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O18" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="P18" t="s">
         <v>207</v>
@@ -2586,16 +2586,16 @@
         <v>211</v>
       </c>
       <c r="C19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F19" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G19" t="s">
         <v>213</v>
@@ -2619,7 +2619,7 @@
         <v>218</v>
       </c>
       <c r="N19" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O19" t="s">
         <v>212</v>
@@ -2642,16 +2642,16 @@
         <v>223</v>
       </c>
       <c r="C20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E20" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F20" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G20" t="s">
         <v>225</v>
@@ -2675,7 +2675,7 @@
         <v>229</v>
       </c>
       <c r="N20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O20" t="s">
         <v>224</v>
@@ -2698,16 +2698,16 @@
         <v>234</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F21" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G21" t="s">
         <v>236</v>
@@ -2731,7 +2731,7 @@
         <v>241</v>
       </c>
       <c r="N21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="O21" t="s">
         <v>235</v>
@@ -2763,7 +2763,7 @@
         <v>254</v>
       </c>
       <c r="F22" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G22" t="s">
         <v>248</v>
@@ -2787,7 +2787,7 @@
         <v>253</v>
       </c>
       <c r="N22" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="O22" t="s">
         <v>247</v>
@@ -2843,10 +2843,10 @@
         <v>264</v>
       </c>
       <c r="N23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="O23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="P23" t="s">
         <v>265</v>
@@ -2855,27 +2855,27 @@
         <v>266</v>
       </c>
       <c r="R23" t="s">
-        <v>267</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" t="s">
         <v>268</v>
       </c>
-      <c r="B24" t="s">
-        <v>269</v>
-      </c>
       <c r="C24" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D24" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E24" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G24" t="s">
         <v>136</v>
@@ -2884,51 +2884,51 @@
         <v>165</v>
       </c>
       <c r="I24" t="s">
+        <v>269</v>
+      </c>
+      <c r="J24" t="s">
         <v>270</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>271</v>
-      </c>
-      <c r="K24" t="s">
-        <v>272</v>
       </c>
       <c r="L24" t="s">
         <v>21</v>
       </c>
       <c r="M24" t="s">
+        <v>272</v>
+      </c>
+      <c r="N24" t="s">
+        <v>382</v>
+      </c>
+      <c r="O24" t="s">
+        <v>383</v>
+      </c>
+      <c r="P24" t="s">
         <v>273</v>
       </c>
-      <c r="N24" t="s">
-        <v>384</v>
-      </c>
-      <c r="O24" t="s">
-        <v>385</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>274</v>
       </c>
-      <c r="Q24" t="s">
-        <v>275</v>
-      </c>
       <c r="R24" t="s">
-        <v>276</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E25" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F25" t="s">
         <v>136</v>
@@ -2943,7 +2943,7 @@
         <v>136</v>
       </c>
       <c r="J25" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K25" t="s">
         <v>136</v>
@@ -2952,13 +2952,13 @@
         <v>136</v>
       </c>
       <c r="M25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P25" t="s">
         <v>136</v>
@@ -2972,226 +2972,226 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F26" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G26" t="s">
         <v>136</v>
       </c>
       <c r="H26" t="s">
+        <v>282</v>
+      </c>
+      <c r="I26" t="s">
+        <v>283</v>
+      </c>
+      <c r="J26" t="s">
         <v>284</v>
       </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>285</v>
-      </c>
-      <c r="J26" t="s">
-        <v>286</v>
-      </c>
-      <c r="K26" t="s">
-        <v>287</v>
       </c>
       <c r="L26" t="s">
         <v>21</v>
       </c>
       <c r="M26" t="s">
+        <v>286</v>
+      </c>
+      <c r="N26" t="s">
+        <v>385</v>
+      </c>
+      <c r="O26" t="s">
+        <v>386</v>
+      </c>
+      <c r="P26" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q26" t="s">
         <v>288</v>
       </c>
-      <c r="N26" t="s">
-        <v>387</v>
-      </c>
-      <c r="O26" t="s">
-        <v>388</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="R26" t="s">
         <v>289</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>290</v>
-      </c>
-      <c r="R26" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C27" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D27" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F27" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G27" t="s">
         <v>136</v>
       </c>
       <c r="H27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I27" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J27" t="s">
         <v>136</v>
       </c>
       <c r="K27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
+        <v>295</v>
+      </c>
+      <c r="N27" t="s">
+        <v>387</v>
+      </c>
+      <c r="O27" t="s">
+        <v>388</v>
+      </c>
+      <c r="P27" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q27" t="s">
         <v>297</v>
       </c>
-      <c r="N27" t="s">
-        <v>389</v>
-      </c>
-      <c r="O27" t="s">
-        <v>390</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="R27" t="s">
         <v>298</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>299</v>
-      </c>
-      <c r="R27" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" t="s">
         <v>301</v>
       </c>
-      <c r="B28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C28" t="s">
-        <v>303</v>
-      </c>
       <c r="D28" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E28" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F28" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G28" t="s">
         <v>136</v>
       </c>
       <c r="H28" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I28" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J28" t="s">
         <v>136</v>
       </c>
       <c r="K28" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
+        <v>305</v>
+      </c>
+      <c r="N28" t="s">
+        <v>389</v>
+      </c>
+      <c r="O28" t="s">
+        <v>390</v>
+      </c>
+      <c r="P28" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q28" t="s">
         <v>307</v>
       </c>
-      <c r="N28" t="s">
-        <v>391</v>
-      </c>
-      <c r="O28" t="s">
-        <v>392</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="R28" t="s">
         <v>308</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>309</v>
-      </c>
-      <c r="R28" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B29" t="s">
+        <v>310</v>
+      </c>
+      <c r="C29" t="s">
         <v>311</v>
       </c>
-      <c r="B29" t="s">
-        <v>312</v>
-      </c>
-      <c r="C29" t="s">
-        <v>313</v>
-      </c>
       <c r="D29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E29" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F29" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G29" t="s">
         <v>136</v>
       </c>
       <c r="H29" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I29" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J29" t="s">
         <v>136</v>
       </c>
       <c r="K29" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L29" t="s">
         <v>136</v>
       </c>
       <c r="M29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="N29" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="O29" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P29" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q29" t="s">
         <v>136</v>
       </c>
       <c r="R29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
